--- a/hrcheck/examples/本月花名册_标准化.xlsx
+++ b/hrcheck/examples/本月花名册_标准化.xlsx
@@ -1251,10 +1251,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>在职</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>离职</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>13869468741</t>
